--- a/ResultForText2/02_flickr8k_text_excel_report.xlsx
+++ b/ResultForText2/02_flickr8k_text_excel_report.xlsx
@@ -79,7 +79,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,14 +497,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.002469</v>
+        <v>0.04321</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>source: flickr8k_ablation_summary.json / 0.image_to_text.R@1</t>
+          <t>source: eval_results.json / image_to_text.R@1</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.016049</v>
+        <v>0.153086</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>source: flickr8k_ablation_summary.json / 0.image_to_text.R@5</t>
+          <t>source: eval_results.json / image_to_text.R@5</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.02963</v>
+        <v>0.224691</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>source: flickr8k_ablation_summary.json / 0.image_to_text.R@10</t>
+          <t>source: eval_results.json / image_to_text.R@10</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.003458</v>
+        <v>0.038775</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>source: flickr8k_ablation_summary.json / 0.text_to_image.R@1</t>
+          <t>source: eval_results.json / text_to_image.R@1</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.014571</v>
+        <v>0.14695</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>source: flickr8k_ablation_summary.json / 0.text_to_image.R@5</t>
+          <t>source: eval_results.json / text_to_image.R@5</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.028896</v>
+        <v>0.23512</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>source: flickr8k_ablation_summary.json / 0.text_to_image.R@10</t>
+          <t>source: eval_results.json / text_to_image.R@10</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>See report.txt for warnings/status notes</t>
+          <t>See retrieval_examples.txt for warnings/status notes</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -751,60 +751,6 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Read from JSON/TXT files only</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>See retrieval_examples.txt for warnings/status notes</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Runtime/file warning</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Read from JSON/TXT files only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>See rubric_report.txt for warnings/status notes</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Runtime/file warning</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Read from JSON/TXT files only</t>
         </is>
@@ -824,15 +770,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -842,18 +784,10 @@
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -864,26 +798,6 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>train_loss</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>val_loss</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>train_top1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>val_top1</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>lr</t>
         </is>
       </c>
     </row>
@@ -892,70 +806,52 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.30755</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2.947902</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.075169</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0.091346</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>3.006647</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Best Epoch: 1.0</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.30755</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>2.947902</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.075169</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.091346</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>2.481877</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Best Epoch by val_top1</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2.095868</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1.784986</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1.478902</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>source: train_history.json</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -967,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1042,11 +938,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>classification_ce</t>
+          <t>train_loss</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3.743837</v>
+        <v>3.431238</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -1062,11 +958,11 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>test_top1</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.0975</v>
+        <v>13.34</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -1082,11 +978,11 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>test_top5</t>
+          <t>batches</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.285</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -1102,11 +998,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>audio_to_text_R@1</t>
+          <t>image_to_text.R@1</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.0975</v>
+        <v>0.003704</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -1122,11 +1018,11 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>audio_to_text_R@5</t>
+          <t>image_to_text.R@5</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.285</v>
+        <v>0.011111</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1142,11 +1038,11 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>audio_to_text_R@10</t>
+          <t>image_to_text.R@10</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.032099</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -1162,11 +1058,11 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>text_to_audio_R@1</t>
+          <t>text_to_image.R@1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.1</v>
+        <v>0.003211</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -1182,11 +1078,11 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>text_to_audio_R@5</t>
+          <t>text_to_image.R@5</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.34</v>
+        <v>0.018276</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -1202,11 +1098,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>text_to_audio_R@10</t>
+          <t>text_to_image.R@10</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.036058</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -1242,11 +1138,11 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>classification_ce</t>
+          <t>train_loss</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3.572714</v>
+        <v>3.385187</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -1262,11 +1158,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>test_top1</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.0975</v>
+        <v>13.16</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -1282,11 +1178,11 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>test_top5</t>
+          <t>batches</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.285</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1302,11 +1198,11 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>audio_to_text_R@1</t>
+          <t>image_to_text.R@1</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.0975</v>
+        <v>0.006173</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -1322,11 +1218,11 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>audio_to_text_R@5</t>
+          <t>image_to_text.R@5</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.285</v>
+        <v>0.01358</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -1342,11 +1238,11 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>audio_to_text_R@10</t>
+          <t>image_to_text.R@10</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.025926</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
@@ -1362,11 +1258,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>text_to_audio_R@1</t>
+          <t>text_to_image.R@1</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.1</v>
+        <v>0.005186</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -1382,11 +1278,11 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>text_to_audio_R@5</t>
+          <t>text_to_image.R@5</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.34</v>
+        <v>0.0163</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
@@ -1402,11 +1298,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>text_to_audio_R@10</t>
+          <t>text_to_image.R@10</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.030625</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -1442,11 +1338,11 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>classification_ce</t>
+          <t>train_loss</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3.539319</v>
+        <v>3.379174</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -1462,11 +1358,11 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>test_top1</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.0975</v>
+        <v>12.99</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
@@ -1482,11 +1378,11 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>test_top5</t>
+          <t>batches</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.285</v>
+        <v>100</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -1502,11 +1398,11 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>audio_to_text_R@1</t>
+          <t>image_to_text.R@1</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0975</v>
+        <v>0.003704</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
@@ -1522,11 +1418,11 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>audio_to_text_R@5</t>
+          <t>image_to_text.R@5</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.285</v>
+        <v>0.014815</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -1542,11 +1438,11 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>audio_to_text_R@10</t>
+          <t>image_to_text.R@10</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.02963</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
@@ -1562,11 +1458,11 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>text_to_audio_R@1</t>
+          <t>text_to_image.R@1</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.1</v>
+        <v>0.001976</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
@@ -1582,11 +1478,11 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>text_to_audio_R@5</t>
+          <t>text_to_image.R@5</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.34</v>
+        <v>0.017535</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
@@ -1602,213 +1498,13 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>text_to_audio_R@10</t>
+          <t>text_to_image.R@10</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.034576</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>classification_ce</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>3.634959</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>test_top1</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>test_top5</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>audio_to_text_R@1</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>audio_to_text_R@5</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>audio_to_text_R@10</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>0.5024999999999999</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>text_to_audio_R@1</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>text_to_audio_R@5</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>source: ablation_summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>temperature=0.2</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>text_to_audio_R@10</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>source: ablation_summary.json</t>
         </is>
@@ -1828,12 +1524,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1870,765 +1566,19 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>airplane</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>0.75</v>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>breathing</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>brushing_teeth</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>can_opening</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>car_horn</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>chainsaw</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>chirping_birds</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>church_bells</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>clapping</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>clock_alarm</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>clock_tick</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>coughing</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>cow</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>crackling_fire</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>crickets</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>crow</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>crying_baby</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>door_wood_creaks</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>door_wood_knock</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>drinking_sipping</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>engine</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>fireworks</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>footsteps</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>frog</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>glass_breaking</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>hand_saw</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>helicopter</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>hen</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>insects</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>keyboard_typing</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>mouse_click</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>pig</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>pouring_water</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>rooster</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>sea_waves</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>sheep</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>siren</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>sneezing</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>snoring</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>thunderstorm</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>toilet_flush</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>vacuum_cleaner</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>washing_machine</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>water_drops</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>source: eval_results.json</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>per_class_accuracy</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr"/>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2703,7 +1653,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.94</v>
+        <v>8.58</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -2743,7 +1693,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.93</v>
+        <v>1.12</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -2783,7 +1733,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.4</v>
+        <v>0.44</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -2803,7 +1753,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -2823,7 +1773,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -2903,7 +1853,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>32.92</v>
+        <v>42</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
@@ -2923,7 +1873,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -2963,7 +1913,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2027.8</v>
+        <v>2002.72</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -3003,7 +1953,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -3023,7 +1973,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
@@ -3043,7 +1993,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.19</v>
+        <v>0.64</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
